--- a/data/nzd0545/nzd0545.xlsx
+++ b/data/nzd0545/nzd0545.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R463"/>
+  <dimension ref="A1:R465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28128,13 +28128,13 @@
         <v>269.72</v>
       </c>
       <c r="L463" t="n">
-        <v>276.1</v>
+        <v>260.53</v>
       </c>
       <c r="M463" t="n">
         <v>276.25</v>
       </c>
       <c r="N463" t="n">
-        <v>276.28</v>
+        <v>270.08</v>
       </c>
       <c r="O463" t="n">
         <v>258.77</v>
@@ -28146,6 +28146,126 @@
         <v>271.41</v>
       </c>
       <c r="R463" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>451.76</v>
+      </c>
+      <c r="C464" t="n">
+        <v>519.09</v>
+      </c>
+      <c r="D464" t="n">
+        <v>321.16</v>
+      </c>
+      <c r="E464" t="n">
+        <v>286.74</v>
+      </c>
+      <c r="F464" t="n">
+        <v>273.09</v>
+      </c>
+      <c r="G464" t="n">
+        <v>280.37</v>
+      </c>
+      <c r="H464" t="n">
+        <v>281.19</v>
+      </c>
+      <c r="I464" t="n">
+        <v>271.49</v>
+      </c>
+      <c r="J464" t="n">
+        <v>266.27</v>
+      </c>
+      <c r="K464" t="n">
+        <v>261.35</v>
+      </c>
+      <c r="L464" t="n">
+        <v>248.24</v>
+      </c>
+      <c r="M464" t="n">
+        <v>261.85</v>
+      </c>
+      <c r="N464" t="n">
+        <v>255.47</v>
+      </c>
+      <c r="O464" t="n">
+        <v>253.91</v>
+      </c>
+      <c r="P464" t="n">
+        <v>258.47</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>265.79</v>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>454.71</v>
+      </c>
+      <c r="C465" t="n">
+        <v>517.5</v>
+      </c>
+      <c r="D465" t="n">
+        <v>316.01</v>
+      </c>
+      <c r="E465" t="n">
+        <v>284.24</v>
+      </c>
+      <c r="F465" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="G465" t="n">
+        <v>279.18</v>
+      </c>
+      <c r="H465" t="n">
+        <v>280.67</v>
+      </c>
+      <c r="I465" t="n">
+        <v>269.94</v>
+      </c>
+      <c r="J465" t="n">
+        <v>262.26</v>
+      </c>
+      <c r="K465" t="n">
+        <v>258.05</v>
+      </c>
+      <c r="L465" t="n">
+        <v>238.79</v>
+      </c>
+      <c r="M465" t="n">
+        <v>249.7</v>
+      </c>
+      <c r="N465" t="n">
+        <v>243.86</v>
+      </c>
+      <c r="O465" t="n">
+        <v>249.37</v>
+      </c>
+      <c r="P465" t="n">
+        <v>254.18</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>260.8</v>
+      </c>
+      <c r="R465" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28162,7 +28282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B515"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33315,6 +33435,26 @@
       </c>
       <c r="B515" t="n">
         <v>-1.1</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>-0.44</v>
       </c>
     </row>
   </sheetData>
@@ -33483,28 +33623,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1016060786344113</v>
+        <v>-0.1044468063056906</v>
       </c>
       <c r="J2" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K2" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004738087061389229</v>
+        <v>0.005052212217322327</v>
       </c>
       <c r="M2" t="n">
-        <v>7.867328849988709</v>
+        <v>7.848098281306325</v>
       </c>
       <c r="N2" t="n">
-        <v>118.9742779462759</v>
+        <v>118.5126847560293</v>
       </c>
       <c r="O2" t="n">
-        <v>10.90753308252035</v>
+        <v>10.88635314308833</v>
       </c>
       <c r="P2" t="n">
-        <v>459.2167359606165</v>
+        <v>459.2474862911413</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33561,28 +33701,28 @@
         <v>0.0386</v>
       </c>
       <c r="I3" t="n">
-        <v>2.13681332189688</v>
+        <v>2.139194975497898</v>
       </c>
       <c r="J3" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K3" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06609148472359927</v>
+        <v>0.06684164219198518</v>
       </c>
       <c r="M3" t="n">
-        <v>40.55641912600125</v>
+        <v>40.3837937909856</v>
       </c>
       <c r="N3" t="n">
-        <v>3508.740386139785</v>
+        <v>3493.385399232868</v>
       </c>
       <c r="O3" t="n">
-        <v>59.23462151596636</v>
+        <v>59.104867813344</v>
       </c>
       <c r="P3" t="n">
-        <v>458.1053662487579</v>
+        <v>458.0793743147565</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33639,28 +33779,28 @@
         <v>0.028</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5375703476797312</v>
+        <v>-0.5296502335363222</v>
       </c>
       <c r="J4" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K4" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1014812546824921</v>
+        <v>0.09944317638995392</v>
       </c>
       <c r="M4" t="n">
-        <v>9.287891570971478</v>
+        <v>9.279047375243154</v>
       </c>
       <c r="N4" t="n">
-        <v>140.129502772785</v>
+        <v>139.9022508862596</v>
       </c>
       <c r="O4" t="n">
-        <v>11.8376307922145</v>
+        <v>11.82802819096487</v>
       </c>
       <c r="P4" t="n">
-        <v>323.9904811852003</v>
+        <v>323.9047841872728</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33717,28 +33857,28 @@
         <v>0.0494</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3664965958703988</v>
+        <v>-0.3678701269356918</v>
       </c>
       <c r="J5" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K5" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05495270766596794</v>
+        <v>0.05585243387505734</v>
       </c>
       <c r="M5" t="n">
-        <v>8.578083814935049</v>
+        <v>8.546906600482961</v>
       </c>
       <c r="N5" t="n">
-        <v>126.3726525394617</v>
+        <v>125.8450854321076</v>
       </c>
       <c r="O5" t="n">
-        <v>11.24155916852559</v>
+        <v>11.21806959472563</v>
       </c>
       <c r="P5" t="n">
-        <v>296.9233348139006</v>
+        <v>296.9382013678235</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -33799,28 +33939,28 @@
         <v>0.0721</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4310994587560551</v>
+        <v>-0.436055508919259</v>
       </c>
       <c r="J6" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K6" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05212965547906667</v>
+        <v>0.05373704878300911</v>
       </c>
       <c r="M6" t="n">
-        <v>10.59317909920325</v>
+        <v>10.57156913851033</v>
       </c>
       <c r="N6" t="n">
-        <v>180.1099374296179</v>
+        <v>179.4505235182852</v>
       </c>
       <c r="O6" t="n">
-        <v>13.42050436569423</v>
+        <v>13.39591443382217</v>
       </c>
       <c r="P6" t="n">
-        <v>289.4499134174424</v>
+        <v>289.5047475521625</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -33881,28 +34021,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08270943776141068</v>
+        <v>-0.0848739685334588</v>
       </c>
       <c r="J7" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K7" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002650637672386713</v>
+        <v>0.002817952265216084</v>
       </c>
       <c r="M7" t="n">
-        <v>9.229804758854719</v>
+        <v>9.200447150815378</v>
       </c>
       <c r="N7" t="n">
-        <v>138.6063302284255</v>
+        <v>138.0280746541097</v>
       </c>
       <c r="O7" t="n">
-        <v>11.77311896773432</v>
+        <v>11.74853500033556</v>
       </c>
       <c r="P7" t="n">
-        <v>284.4288749688505</v>
+        <v>284.4526199565206</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -33963,28 +34103,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01088545977386834</v>
+        <v>0.01031889905144362</v>
       </c>
       <c r="J8" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K8" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L8" t="n">
-        <v>9.301303319031451e-05</v>
+        <v>8.440990696889639e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.221276955704319</v>
+        <v>6.197389191738939</v>
       </c>
       <c r="N8" t="n">
-        <v>69.32356116747715</v>
+        <v>69.02616913617813</v>
       </c>
       <c r="O8" t="n">
-        <v>8.326077177607541</v>
+        <v>8.308198910484638</v>
       </c>
       <c r="P8" t="n">
-        <v>281.2775543327475</v>
+        <v>281.2837095765654</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -34045,28 +34185,28 @@
         <v>0.1322</v>
       </c>
       <c r="I9" t="n">
-        <v>8.836584719557153e-05</v>
+        <v>-0.003034973854257092</v>
       </c>
       <c r="J9" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K9" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L9" t="n">
-        <v>5.763120536350641e-09</v>
+        <v>6.860224298743667e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>6.619495533741021</v>
+        <v>6.605806222770315</v>
       </c>
       <c r="N9" t="n">
-        <v>74.12418562470017</v>
+        <v>73.86148823758664</v>
       </c>
       <c r="O9" t="n">
-        <v>8.609540384056524</v>
+        <v>8.594270663505231</v>
       </c>
       <c r="P9" t="n">
-        <v>274.2831341465809</v>
+        <v>274.3169323355471</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -34127,28 +34267,28 @@
         <v>0.0518</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04374719521454177</v>
+        <v>0.04622510595116765</v>
       </c>
       <c r="J10" t="n">
+        <v>464</v>
+      </c>
+      <c r="K10" t="n">
         <v>462</v>
       </c>
-      <c r="K10" t="n">
-        <v>460</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0004359236536445321</v>
+        <v>0.0004914207360721123</v>
       </c>
       <c r="M10" t="n">
-        <v>12.79819882099643</v>
+        <v>12.75734179008234</v>
       </c>
       <c r="N10" t="n">
-        <v>236.6706293235598</v>
+        <v>235.6969652207682</v>
       </c>
       <c r="O10" t="n">
-        <v>15.38410313679546</v>
+        <v>15.35242538561149</v>
       </c>
       <c r="P10" t="n">
-        <v>260.2881578910216</v>
+        <v>260.261088973765</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34205,28 +34345,28 @@
         <v>0.027</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2502768522832905</v>
+        <v>-0.2482808311578786</v>
       </c>
       <c r="J11" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K11" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01344625212188011</v>
+        <v>0.01336338316587726</v>
       </c>
       <c r="M11" t="n">
-        <v>13.25220301144597</v>
+        <v>13.20490582254759</v>
       </c>
       <c r="N11" t="n">
-        <v>249.5079011648475</v>
+        <v>248.4638029053415</v>
       </c>
       <c r="O11" t="n">
-        <v>15.79581910395429</v>
+        <v>15.76273462649617</v>
       </c>
       <c r="P11" t="n">
-        <v>264.1674545583071</v>
+        <v>264.1457504219399</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34283,28 +34423,28 @@
         <v>0.0372</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07966836756399236</v>
+        <v>-0.1000788915969344</v>
       </c>
       <c r="J12" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K12" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000681174413920127</v>
+        <v>0.001084284866474605</v>
       </c>
       <c r="M12" t="n">
-        <v>17.69321287075334</v>
+        <v>17.65894453006691</v>
       </c>
       <c r="N12" t="n">
-        <v>500.0957735264905</v>
+        <v>498.333307124404</v>
       </c>
       <c r="O12" t="n">
-        <v>22.36282123361206</v>
+        <v>22.32338027997561</v>
       </c>
       <c r="P12" t="n">
-        <v>260.8375551038398</v>
+        <v>261.0613839247661</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34361,28 +34501,28 @@
         <v>0.0323</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6026301341602556</v>
+        <v>-0.6047709430734833</v>
       </c>
       <c r="J13" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K13" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05841481404171278</v>
+        <v>0.05932487547014964</v>
       </c>
       <c r="M13" t="n">
-        <v>13.35031212226793</v>
+        <v>13.32188352486576</v>
       </c>
       <c r="N13" t="n">
-        <v>314.3937565198477</v>
+        <v>313.208940338121</v>
       </c>
       <c r="O13" t="n">
-        <v>17.73115214868587</v>
+        <v>17.69771003090855</v>
       </c>
       <c r="P13" t="n">
-        <v>274.3916639654847</v>
+        <v>274.4151870341061</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34439,28 +34579,28 @@
         <v>0.035</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1315439148003842</v>
+        <v>-0.1439485977811551</v>
       </c>
       <c r="J14" t="n">
+        <v>464</v>
+      </c>
+      <c r="K14" t="n">
         <v>462</v>
       </c>
-      <c r="K14" t="n">
-        <v>460</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.003045146786320729</v>
+        <v>0.003676710445446707</v>
       </c>
       <c r="M14" t="n">
-        <v>13.52366719744298</v>
+        <v>13.5062465428257</v>
       </c>
       <c r="N14" t="n">
-        <v>305.9068344650481</v>
+        <v>304.8975202771435</v>
       </c>
       <c r="O14" t="n">
-        <v>17.4901925222408</v>
+        <v>17.46131496414699</v>
       </c>
       <c r="P14" t="n">
-        <v>264.1482445857197</v>
+        <v>264.2836298041186</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34517,28 +34657,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1957213966690555</v>
+        <v>-0.1979344874920045</v>
       </c>
       <c r="J15" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K15" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01696125026846762</v>
+        <v>0.01750188174961309</v>
       </c>
       <c r="M15" t="n">
-        <v>8.780329813439712</v>
+        <v>8.753779554567565</v>
       </c>
       <c r="N15" t="n">
-        <v>121.4613636050169</v>
+        <v>120.9871828913621</v>
       </c>
       <c r="O15" t="n">
-        <v>11.02095112070718</v>
+        <v>10.99941738872392</v>
       </c>
       <c r="P15" t="n">
-        <v>259.4371744267821</v>
+        <v>259.4611290185227</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34595,28 +34735,28 @@
         <v>0.0376</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2364071632876039</v>
+        <v>-0.2362742295228099</v>
       </c>
       <c r="J16" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K16" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02381242431076303</v>
+        <v>0.0240120990384235</v>
       </c>
       <c r="M16" t="n">
-        <v>8.90859434726843</v>
+        <v>8.879335141776016</v>
       </c>
       <c r="N16" t="n">
-        <v>125.5646251546752</v>
+        <v>125.0421532399763</v>
       </c>
       <c r="O16" t="n">
-        <v>11.20556224179203</v>
+        <v>11.18222487879654</v>
       </c>
       <c r="P16" t="n">
-        <v>262.5345261622828</v>
+        <v>262.5330963693457</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34673,28 +34813,28 @@
         <v>0.0414</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3026550087640988</v>
+        <v>-0.3005537772642197</v>
       </c>
       <c r="J17" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K17" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04060029586443403</v>
+        <v>0.04042418917314816</v>
       </c>
       <c r="M17" t="n">
-        <v>8.612872935308067</v>
+        <v>8.585053411837004</v>
       </c>
       <c r="N17" t="n">
-        <v>118.6267113064733</v>
+        <v>118.1657945059119</v>
       </c>
       <c r="O17" t="n">
-        <v>10.89158901659778</v>
+        <v>10.87040912320746</v>
       </c>
       <c r="P17" t="n">
-        <v>269.0318543861316</v>
+        <v>269.0091377874666</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34732,7 +34872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R463"/>
+  <dimension ref="A1:R465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77113,7 +77253,7 @@
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>-46.55981735527289,169.55409020808656</t>
+          <t>-46.559679718726436,169.55412735589647</t>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -77123,7 +77263,7 @@
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t>-46.55962848980762,169.5523047669582</t>
+          <t>-46.55957356224851,169.55231858794468</t>
         </is>
       </c>
       <c r="O463" t="inlineStr">
@@ -77142,6 +77282,190 @@
         </is>
       </c>
       <c r="R463" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>-46.56226563551711,169.5625813603702</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>-46.56277663938298,169.5615438176732</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>-46.560936596244204,169.56108900449075</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-46.56054577358633,169.5602750016898</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-46.56033903945733,169.55941537437053</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>-46.56031781105824,169.55850976580817</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-46.56023982087428,169.5576232161639</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>-46.560060685357136,169.5567637408141</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>-46.559919887281524,169.55588903903202</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>-46.55978168130202,169.55501308800885</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>-46.55957107689119,169.5541566779456</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>-46.55959667326886,169.55323651801464</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>-46.55944412810194,169.55235115630794</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>-46.559346530785795,169.55142076054045</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>-46.55934012467793,169.550488124693</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>-46.559360518385574,169.5495823855699</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>-46.5622917819597,169.56257488011607</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>-46.56276254692569,169.56154731065268</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>-46.56089095086826,169.56110031789623</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-46.56052361566944,169.56028049380413</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-46.56032583336048,169.5594186477956</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-46.560307263926084,169.55851238027367</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-46.56023521744296,169.557624403474</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-46.56004698190168,169.5567674259518</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>-46.5598844393291,169.55589860556313</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>-46.55975250972321,169.55502096100923</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>-46.55948754023972,169.55417922410382</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>-46.559489269214104,169.55326550718956</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>-46.55934127179754,169.5523770369995</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>-46.55930605999413,169.55142851199705</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>-46.55930175504641,169.55049388081628</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>-46.55931588803186,169.549589081433</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0545/nzd0545.xlsx
+++ b/data/nzd0545/nzd0545.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R465"/>
+  <dimension ref="A1:R468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28128,13 +28128,13 @@
         <v>269.72</v>
       </c>
       <c r="L463" t="n">
-        <v>260.53</v>
+        <v>276.1</v>
       </c>
       <c r="M463" t="n">
         <v>276.25</v>
       </c>
       <c r="N463" t="n">
-        <v>270.08</v>
+        <v>276.28</v>
       </c>
       <c r="O463" t="n">
         <v>258.77</v>
@@ -28188,13 +28188,13 @@
         <v>261.35</v>
       </c>
       <c r="L464" t="n">
-        <v>248.24</v>
+        <v>274.96</v>
       </c>
       <c r="M464" t="n">
-        <v>261.85</v>
+        <v>274.59</v>
       </c>
       <c r="N464" t="n">
-        <v>255.47</v>
+        <v>274.41</v>
       </c>
       <c r="O464" t="n">
         <v>253.91</v>
@@ -28248,13 +28248,13 @@
         <v>258.05</v>
       </c>
       <c r="L465" t="n">
-        <v>238.79</v>
+        <v>274.96</v>
       </c>
       <c r="M465" t="n">
-        <v>249.7</v>
+        <v>274.59</v>
       </c>
       <c r="N465" t="n">
-        <v>243.86</v>
+        <v>274.41</v>
       </c>
       <c r="O465" t="n">
         <v>249.37</v>
@@ -28268,6 +28268,186 @@
       <c r="R465" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:49+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>453.47</v>
+      </c>
+      <c r="C466" t="n">
+        <v>514.83</v>
+      </c>
+      <c r="D466" t="n">
+        <v>313.21</v>
+      </c>
+      <c r="E466" t="n">
+        <v>282.76</v>
+      </c>
+      <c r="F466" t="n">
+        <v>270.65</v>
+      </c>
+      <c r="G466" t="n">
+        <v>278.59</v>
+      </c>
+      <c r="H466" t="n">
+        <v>280.5</v>
+      </c>
+      <c r="I466" t="n">
+        <v>269.22</v>
+      </c>
+      <c r="J466" t="n">
+        <v>261.17</v>
+      </c>
+      <c r="K466" t="n">
+        <v>257.09</v>
+      </c>
+      <c r="L466" t="n">
+        <v>271.76</v>
+      </c>
+      <c r="M466" t="n">
+        <v>271.21</v>
+      </c>
+      <c r="N466" t="n">
+        <v>270.67</v>
+      </c>
+      <c r="O466" t="n">
+        <v>247.53</v>
+      </c>
+      <c r="P466" t="n">
+        <v>252.18</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>258.18</v>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>457.73</v>
+      </c>
+      <c r="C467" t="n">
+        <v>514.83</v>
+      </c>
+      <c r="D467" t="n">
+        <v>309.58</v>
+      </c>
+      <c r="E467" t="n">
+        <v>281.41</v>
+      </c>
+      <c r="F467" t="n">
+        <v>267.63</v>
+      </c>
+      <c r="G467" t="n">
+        <v>276.19</v>
+      </c>
+      <c r="H467" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="I467" t="n">
+        <v>266.93</v>
+      </c>
+      <c r="J467" t="n">
+        <v>257</v>
+      </c>
+      <c r="K467" t="n">
+        <v>251</v>
+      </c>
+      <c r="L467" t="n">
+        <v>259.26</v>
+      </c>
+      <c r="M467" t="n">
+        <v>263.15</v>
+      </c>
+      <c r="N467" t="n">
+        <v>259.98</v>
+      </c>
+      <c r="O467" t="n">
+        <v>243.26</v>
+      </c>
+      <c r="P467" t="n">
+        <v>248.39</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>253.84</v>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>459.74</v>
+      </c>
+      <c r="C468" t="n">
+        <v>490.03</v>
+      </c>
+      <c r="D468" t="n">
+        <v>305.36</v>
+      </c>
+      <c r="E468" t="n">
+        <v>281.29</v>
+      </c>
+      <c r="F468" t="n">
+        <v>268.66</v>
+      </c>
+      <c r="G468" t="n">
+        <v>276.88</v>
+      </c>
+      <c r="H468" t="n">
+        <v>279.97</v>
+      </c>
+      <c r="I468" t="n">
+        <v>268.28</v>
+      </c>
+      <c r="J468" t="n">
+        <v>258.97</v>
+      </c>
+      <c r="K468" t="n">
+        <v>250.67</v>
+      </c>
+      <c r="L468" t="n">
+        <v>256.23</v>
+      </c>
+      <c r="M468" t="n">
+        <v>260.21</v>
+      </c>
+      <c r="N468" t="n">
+        <v>255.52</v>
+      </c>
+      <c r="O468" t="n">
+        <v>240.91</v>
+      </c>
+      <c r="P468" t="n">
+        <v>247.11</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>253.56</v>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28282,7 +28462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33455,6 +33635,36 @@
       </c>
       <c r="B517" t="n">
         <v>-0.44</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -33623,28 +33833,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1044468063056906</v>
+        <v>-0.1037130689162357</v>
       </c>
       <c r="J2" t="n">
+        <v>467</v>
+      </c>
+      <c r="K2" t="n">
         <v>464</v>
       </c>
-      <c r="K2" t="n">
-        <v>461</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.005052212217322327</v>
+        <v>0.005053680635867197</v>
       </c>
       <c r="M2" t="n">
-        <v>7.848098281306325</v>
+        <v>7.813440522113493</v>
       </c>
       <c r="N2" t="n">
-        <v>118.5126847560293</v>
+        <v>117.7926475150626</v>
       </c>
       <c r="O2" t="n">
-        <v>10.88635314308833</v>
+        <v>10.85323212296976</v>
       </c>
       <c r="P2" t="n">
-        <v>459.2474862911413</v>
+        <v>459.2394561283364</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33701,28 +33911,28 @@
         <v>0.0386</v>
       </c>
       <c r="I3" t="n">
-        <v>2.139194975497898</v>
+        <v>2.126770333222348</v>
       </c>
       <c r="J3" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K3" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06684164219198518</v>
+        <v>0.06701586408837856</v>
       </c>
       <c r="M3" t="n">
-        <v>40.3837937909856</v>
+        <v>40.21388727445719</v>
       </c>
       <c r="N3" t="n">
-        <v>3493.385399232868</v>
+        <v>3472.019595031415</v>
       </c>
       <c r="O3" t="n">
-        <v>59.104867813344</v>
+        <v>58.92384572506631</v>
       </c>
       <c r="P3" t="n">
-        <v>458.0793743147565</v>
+        <v>458.2159936615126</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33779,28 +33989,28 @@
         <v>0.028</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5296502335363222</v>
+        <v>-0.5299072360475272</v>
       </c>
       <c r="J4" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K4" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09944317638995392</v>
+        <v>0.1008223950899589</v>
       </c>
       <c r="M4" t="n">
-        <v>9.279047375243154</v>
+        <v>9.236342707255544</v>
       </c>
       <c r="N4" t="n">
-        <v>139.9022508862596</v>
+        <v>139.0675575821759</v>
       </c>
       <c r="O4" t="n">
-        <v>11.82802819096487</v>
+        <v>11.79269085417641</v>
       </c>
       <c r="P4" t="n">
-        <v>323.9047841872728</v>
+        <v>323.9076317917259</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33857,28 +34067,28 @@
         <v>0.0494</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3678701269356918</v>
+        <v>-0.3745933975026881</v>
       </c>
       <c r="J5" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K5" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05585243387505734</v>
+        <v>0.05853095684455945</v>
       </c>
       <c r="M5" t="n">
-        <v>8.546906600482961</v>
+        <v>8.520120302289078</v>
       </c>
       <c r="N5" t="n">
-        <v>125.8450854321076</v>
+        <v>125.2072648120605</v>
       </c>
       <c r="O5" t="n">
-        <v>11.21806959472563</v>
+        <v>11.18960521252026</v>
       </c>
       <c r="P5" t="n">
-        <v>296.9382013678235</v>
+        <v>297.011396790823</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -33939,28 +34149,28 @@
         <v>0.0721</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.436055508919259</v>
+        <v>-0.4477471975766871</v>
       </c>
       <c r="J6" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K6" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05373704878300911</v>
+        <v>0.05714539402763097</v>
       </c>
       <c r="M6" t="n">
-        <v>10.57156913851033</v>
+        <v>10.5601114133937</v>
       </c>
       <c r="N6" t="n">
-        <v>179.4505235182852</v>
+        <v>178.7719475430714</v>
       </c>
       <c r="O6" t="n">
-        <v>13.39591443382217</v>
+        <v>13.37056272350088</v>
       </c>
       <c r="P6" t="n">
-        <v>289.5047475521625</v>
+        <v>289.6348813450667</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -34021,28 +34231,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0848739685334588</v>
+        <v>-0.09140959763411793</v>
       </c>
       <c r="J7" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K7" t="n">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002817952265216084</v>
+        <v>0.003312214463913832</v>
       </c>
       <c r="M7" t="n">
-        <v>9.200447150815378</v>
+        <v>9.17303356516555</v>
       </c>
       <c r="N7" t="n">
-        <v>138.0280746541097</v>
+        <v>137.2915594231715</v>
       </c>
       <c r="O7" t="n">
-        <v>11.74853500033556</v>
+        <v>11.71714809256807</v>
       </c>
       <c r="P7" t="n">
-        <v>284.4526199565206</v>
+        <v>284.5247481019895</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -34103,28 +34313,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01031889905144362</v>
+        <v>0.008175101102924191</v>
       </c>
       <c r="J8" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K8" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L8" t="n">
-        <v>8.440990696889639e-05</v>
+        <v>5.376025290981801e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.197389191738939</v>
+        <v>6.168585945059853</v>
       </c>
       <c r="N8" t="n">
-        <v>69.02616913617813</v>
+        <v>68.60026990110207</v>
       </c>
       <c r="O8" t="n">
-        <v>8.308198910484638</v>
+        <v>8.282527989756634</v>
       </c>
       <c r="P8" t="n">
-        <v>281.2837095765654</v>
+        <v>281.3071386438053</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -34185,28 +34395,28 @@
         <v>0.1322</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.003034973854257092</v>
+        <v>-0.01096210914981009</v>
       </c>
       <c r="J9" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K9" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L9" t="n">
-        <v>6.860224298743667e-06</v>
+        <v>9.053291447347345e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>6.605806222770315</v>
+        <v>6.600311773207619</v>
       </c>
       <c r="N9" t="n">
-        <v>73.86148823758664</v>
+        <v>73.62601482876823</v>
       </c>
       <c r="O9" t="n">
-        <v>8.594270663505231</v>
+        <v>8.580560286413016</v>
       </c>
       <c r="P9" t="n">
-        <v>274.3169323355471</v>
+        <v>274.4032273932875</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -34267,28 +34477,28 @@
         <v>0.0518</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04622510595116765</v>
+        <v>0.04297240620696447</v>
       </c>
       <c r="J10" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K10" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0004914207360721123</v>
+        <v>0.0004310017977903202</v>
       </c>
       <c r="M10" t="n">
-        <v>12.75734179008234</v>
+        <v>12.68754630647235</v>
       </c>
       <c r="N10" t="n">
-        <v>235.6969652207682</v>
+        <v>234.2335554976627</v>
       </c>
       <c r="O10" t="n">
-        <v>15.35242538561149</v>
+        <v>15.30469063711066</v>
       </c>
       <c r="P10" t="n">
-        <v>260.261088973765</v>
+        <v>260.2968525209471</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34345,28 +34555,28 @@
         <v>0.027</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2482808311578786</v>
+        <v>-0.2541910319105678</v>
       </c>
       <c r="J11" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K11" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01336338316587726</v>
+        <v>0.01419461245766007</v>
       </c>
       <c r="M11" t="n">
-        <v>13.20490582254759</v>
+        <v>13.14801653086288</v>
       </c>
       <c r="N11" t="n">
-        <v>248.4638029053415</v>
+        <v>247.0480545677108</v>
       </c>
       <c r="O11" t="n">
-        <v>15.76273462649617</v>
+        <v>15.71776239061117</v>
       </c>
       <c r="P11" t="n">
-        <v>264.1457504219399</v>
+        <v>264.2104557869056</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34423,28 +34633,28 @@
         <v>0.0372</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1000788915969344</v>
+        <v>-0.06055734155232299</v>
       </c>
       <c r="J12" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K12" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001084284866474605</v>
+        <v>0.0004023704934844607</v>
       </c>
       <c r="M12" t="n">
-        <v>17.65894453006691</v>
+        <v>17.59516998545953</v>
       </c>
       <c r="N12" t="n">
-        <v>498.333307124404</v>
+        <v>496.1836121992682</v>
       </c>
       <c r="O12" t="n">
-        <v>22.32338027997561</v>
+        <v>22.27517928545735</v>
       </c>
       <c r="P12" t="n">
-        <v>261.0613839247661</v>
+        <v>260.6275566933582</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34501,28 +34711,28 @@
         <v>0.0323</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6047709430734833</v>
+        <v>-0.579353342380447</v>
       </c>
       <c r="J13" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K13" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05932487547014964</v>
+        <v>0.05525696801016777</v>
       </c>
       <c r="M13" t="n">
-        <v>13.32188352486576</v>
+        <v>13.28162530510161</v>
       </c>
       <c r="N13" t="n">
-        <v>313.208940338121</v>
+        <v>312.5528054044284</v>
       </c>
       <c r="O13" t="n">
-        <v>17.69771003090855</v>
+        <v>17.67916302895667</v>
       </c>
       <c r="P13" t="n">
-        <v>274.4151870341061</v>
+        <v>274.1356471302452</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34579,28 +34789,28 @@
         <v>0.035</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1439485977811551</v>
+        <v>-0.1176854867429885</v>
       </c>
       <c r="J14" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K14" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003676710445446707</v>
+        <v>0.002491079528996298</v>
       </c>
       <c r="M14" t="n">
-        <v>13.5062465428257</v>
+        <v>13.46281674199369</v>
       </c>
       <c r="N14" t="n">
-        <v>304.8975202771435</v>
+        <v>303.6957572483869</v>
       </c>
       <c r="O14" t="n">
-        <v>17.46131496414699</v>
+        <v>17.42686883087111</v>
       </c>
       <c r="P14" t="n">
-        <v>264.2836298041186</v>
+        <v>263.9968942774011</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34657,28 +34867,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1979344874920045</v>
+        <v>-0.2112211886803951</v>
       </c>
       <c r="J15" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K15" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01750188174961309</v>
+        <v>0.02005817526021458</v>
       </c>
       <c r="M15" t="n">
-        <v>8.753779554567565</v>
+        <v>8.763989504033333</v>
       </c>
       <c r="N15" t="n">
-        <v>120.9871828913621</v>
+        <v>120.9129197250659</v>
       </c>
       <c r="O15" t="n">
-        <v>10.99941738872392</v>
+        <v>10.99604109327834</v>
       </c>
       <c r="P15" t="n">
-        <v>259.4611290185227</v>
+        <v>259.6058036147913</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34735,28 +34945,28 @@
         <v>0.0376</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2362742295228099</v>
+        <v>-0.2452711843221796</v>
       </c>
       <c r="J16" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K16" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0240120990384235</v>
+        <v>0.02613504309446135</v>
       </c>
       <c r="M16" t="n">
-        <v>8.879335141776016</v>
+        <v>8.867800876648722</v>
       </c>
       <c r="N16" t="n">
-        <v>125.0421532399763</v>
+        <v>124.567874867137</v>
       </c>
       <c r="O16" t="n">
-        <v>11.18222487879654</v>
+        <v>11.16099793330045</v>
       </c>
       <c r="P16" t="n">
-        <v>262.5330963693457</v>
+        <v>262.6310229583491</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34813,28 +35023,28 @@
         <v>0.0414</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3005537772642197</v>
+        <v>-0.3079549473622007</v>
       </c>
       <c r="J17" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K17" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04042418917314816</v>
+        <v>0.04287794819426549</v>
       </c>
       <c r="M17" t="n">
-        <v>8.585053411837004</v>
+        <v>8.570637735971498</v>
       </c>
       <c r="N17" t="n">
-        <v>118.1657945059119</v>
+        <v>117.6373355277813</v>
       </c>
       <c r="O17" t="n">
-        <v>10.87040912320746</v>
+        <v>10.84607465988416</v>
       </c>
       <c r="P17" t="n">
-        <v>269.0091377874666</v>
+        <v>269.0896961741645</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34872,7 +35082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R465"/>
+  <dimension ref="A1:R468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77253,7 +77463,7 @@
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>-46.559679718726436,169.55412735589647</t>
+          <t>-46.55981735527289,169.55409020808656</t>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -77263,7 +77473,7 @@
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t>-46.55957356224851,169.55231858794468</t>
+          <t>-46.55962848980762,169.5523047669582</t>
         </is>
       </c>
       <c r="O463" t="inlineStr">
@@ -77345,17 +77555,17 @@
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>-46.55957107689119,169.5541566779456</t>
+          <t>-46.559807277838566,169.5540929279718</t>
         </is>
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>-46.55959667326886,169.55323651801464</t>
+          <t>-46.55970929281614,169.55320612099928</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t>-46.55944412810194,169.55235115630794</t>
+          <t>-46.559611922947354,169.55230893554932</t>
         </is>
       </c>
       <c r="O464" t="inlineStr">
@@ -77437,17 +77647,17 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>-46.55948754023972,169.55417922410382</t>
+          <t>-46.559807277838566,169.5540929279718</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>-46.559489269214104,169.55326550718956</t>
+          <t>-46.55970929281614,169.55320612099928</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t>-46.55934127179754,169.5523770369995</t>
+          <t>-46.559611922947354,169.55230893554932</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
@@ -77468,6 +77678,282 @@
       <c r="R465" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:49+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>-46.562280791590695,169.56257760402033</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>-46.56273888223283,169.5615531762175</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>-46.560866133964026,169.5611064688651</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-46.560510498182424,169.56028374513346</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-46.560317413365745,169.5594207348778</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>-46.560302034675644,169.55851367652085</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-46.56023371247502,169.55762479163303</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-46.56004061642551,169.556769137757</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>-46.55987480385053,169.55590120593953</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>-46.55974402344557,169.5550232513349</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>-46.55977899030304,169.55410056273135</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>-46.55967941416204,169.5532141855271</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>-46.55957878922604,169.55231727272312</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>-46.55928965773465,169.55143165355278</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>-46.55928386710605,169.55049656432033</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>-46.5592924548598,169.5495925970914</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>-46.5623185488257,169.56256824608604</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>-46.56273888223283,169.5615531762175</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>-46.56083396061948,169.5611144431476</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-46.56049853290697,169.56028671087157</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-46.56029064664521,169.55942736959747</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>-46.5602807631482,169.55851894938786</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>-46.560223089171885,169.5576275315784</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>-46.56002037067468,169.55677458224557</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>-46.5598379415142,169.55591115415913</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>-46.55969018862005,169.5550377805698</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>-46.559668492109374,169.5541303859271</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>-46.55960816506001,169.55323341628474</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>-46.55948408347675,169.5523411027111</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>-46.55925159379487,169.55143894400254</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>-46.55924996945866,169.5505016495548</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>-46.55925363807799,169.54959842073131</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>-46.56233636385867,169.56256383071764</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>-46.56251907532311,169.56160765759705</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>-46.56079655799733,169.5611237135124</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-46.56049746932691,169.56028697449264</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-46.56029977569236,169.5594251067634</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>-46.56028687871239,169.55851743343908</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>-46.56022902051615,169.5576260017757</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-46.56003230594268,169.5567713726131</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>-46.55985535609534,169.55590645440256</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>-46.559687271461925,169.55503856786734</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>-46.55964170734529,169.5541376150496</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>-46.55958217593214,169.5532404309641</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>-46.559444571066194,169.55235104484908</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>-46.559230645256164,169.551442956306</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>-46.55923852117657,169.55050336699375</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>-46.559251133769465,169.54959879644966</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
